--- a/docs/compatibility/uwp_compatibility_list.xlsx
+++ b/docs/compatibility/uwp_compatibility_list.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
